--- a/output/pdf_financials_xlsx/KCP.xlsx
+++ b/output/pdf_financials_xlsx/KCP.xlsx
@@ -3457,10 +3457,10 @@
         <v>5.134536</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.488543</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>8.5703</v>
       </c>
     </row>
     <row r="93">
@@ -5200,7 +5200,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KCP.xlsx
+++ b/output/pdf_financials_xlsx/KCP.xlsx
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.035394</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.055916</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.074934</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -792,13 +792,13 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.062</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002917</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.12681</v>
       </c>
     </row>
     <row r="13">
@@ -1299,13 +1299,13 @@
         <v>-0.92714</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.214883</v>
+        <v>-5.250277</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-8.466037999999999</v>
+        <v>-8.521953999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.165544</v>
+        <v>-6.240478</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1313,13 +1313,13 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.47929</v>
+        <v>-5.41729</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.249481</v>
+        <v>-5.252398</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-7.56886</v>
+        <v>-7.69567</v>
       </c>
     </row>
     <row r="28">
@@ -1365,13 +1365,13 @@
         <v>-0.92714</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.214883</v>
+        <v>-5.250277</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.466037999999999</v>
+        <v>-8.521953999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.165544</v>
+        <v>-6.240478</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.47929</v>
+        <v>-5.41729</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.249481</v>
+        <v>-5.252398</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-7.56886</v>
+        <v>-7.69567</v>
       </c>
     </row>
     <row r="30">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.022965</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.360725</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>10.005656</v>
@@ -1544,13 +1544,13 @@
         <v>0.020664</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.022172</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.028949</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>15.695101</v>
       </c>
     </row>
     <row r="35">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.022965</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.360725</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>10.005656</v>
@@ -1606,13 +1606,13 @@
         <v>0.020664</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.022172</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.028949</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>15.695101</v>
       </c>
     </row>
     <row r="37">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.023444</v>
+        <v>0.000479</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.68582</v>
+        <v>0.325095</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.343478</v>
@@ -1978,13 +1978,13 @@
         <v>0.094888</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.087376</v>
+        <v>0.065204</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.124334</v>
+        <v>0.095385</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>15.84263</v>
+        <v>0.147529</v>
       </c>
     </row>
     <row r="49">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">

--- a/output/pdf_financials_xlsx/KCP.xlsx
+++ b/output/pdf_financials_xlsx/KCP.xlsx
@@ -522,10 +522,8 @@
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -555,10 +553,8 @@
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -588,10 +584,8 @@
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -610,10 +604,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.432904</v>
+        <v>0.456085</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.936852</v>
+        <v>1.02181</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2.005866</v>
@@ -621,19 +615,17 @@
       <c r="E7" s="3" t="n">
         <v>0.7369599999999999</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F7" s="3" t="n">
+        <v>0.7299600000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.100455</v>
+        <v>1.220657</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.427896</v>
+        <v>0.467633</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.40133</v>
+        <v>1.481139</v>
       </c>
     </row>
     <row r="8">
@@ -654,10 +646,8 @@
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -687,10 +677,8 @@
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -709,10 +697,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.432904</v>
+        <v>0.456085</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.936852</v>
+        <v>1.02181</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>2.005866</v>
@@ -720,10 +708,8 @@
       <c r="E10" s="3" t="n">
         <v>0.7369599999999999</v>
       </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F10" s="3" t="n">
+        <v>4.062351</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>4.683762</v>
@@ -753,10 +739,8 @@
       <c r="E11" s="3" t="n">
         <v>-6.240478</v>
       </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" s="3" t="n">
+        <v>-4.062351</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-4.683762</v>
@@ -784,12 +768,10 @@
         <v>0.055916</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.074934</v>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.074934</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-0.030795</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>-0.062</v>
@@ -819,10 +801,8 @@
       <c r="E13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
@@ -852,10 +832,8 @@
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -885,10 +863,8 @@
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -918,10 +894,8 @@
       <c r="E16" s="3" t="n">
         <v>-6.165544</v>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" s="3" t="n">
+        <v>-4.062351</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-5.47929</v>
@@ -951,10 +925,8 @@
       <c r="E17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1078,10 +1050,8 @@
       <c r="E20" s="3" t="n">
         <v>-6.165544</v>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F20" s="3" t="n">
+        <v>-4.062351</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-5.47929</v>
@@ -1111,10 +1081,8 @@
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1144,10 +1112,8 @@
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0</v>
@@ -1178,7 +1144,7 @@
         <v>-6.165544</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-5.47929</v>
+        <v>-4.062351</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-5.47929</v>
@@ -1208,10 +1174,8 @@
       <c r="E24" s="3" t="n">
         <v>-0.09</v>
       </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F24" s="3" t="n">
+        <v>-0.06</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>-0.07000000000000001</v>
@@ -1241,10 +1205,8 @@
       <c r="E25" s="3" t="n">
         <v>-0.09</v>
       </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F25" s="3" t="n">
+        <v>-0.06</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>-0.07000000000000001</v>
@@ -1274,10 +1236,8 @@
       <c r="E26" s="3" t="n">
         <v>68.506044</v>
       </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="3" t="n">
+        <v>67.70585</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>78.275571</v>
@@ -1305,12 +1265,10 @@
         <v>-8.521953999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.240478</v>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.09061</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-4.031556</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-5.41729</v>
@@ -1340,10 +1298,8 @@
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -1371,12 +1327,10 @@
         <v>-8.521953999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.240478</v>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.09061</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-4.031556</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-5.41729</v>
@@ -1453,10 +1407,8 @@
       <c r="E31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -4815,7 +4767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L149"/>
+  <dimension ref="A1:L150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10741,10 +10693,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="5" t="n">
+        <v>0.107707</v>
       </c>
       <c r="J109" s="5" t="n">
         <v>0.085068</v>
@@ -10789,10 +10739,8 @@
       <c r="H110" s="5" t="n">
         <v>0.088861</v>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I110" s="5" t="n">
+        <v>0.14566</v>
       </c>
       <c r="J110" s="5" t="n">
         <v>0.176892</v>
@@ -10891,10 +10839,8 @@
       <c r="H112" s="5" t="n">
         <v>0.045034</v>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I112" s="5" t="n">
+        <v>-0.007469</v>
       </c>
       <c r="J112" s="5" t="n">
         <v>-0.017204</v>
@@ -10941,10 +10887,8 @@
       <c r="H113" s="5" t="n">
         <v>0.1335</v>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I113" s="5" t="n">
+        <v>0.101438</v>
       </c>
       <c r="J113" s="5" t="n">
         <v>0.08400000000000001</v>
@@ -10989,10 +10933,8 @@
       <c r="H114" s="5" t="n">
         <v>0.26583</v>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I114" s="5" t="n">
+        <v>0.344331</v>
       </c>
       <c r="J114" s="5" t="n">
         <v>0.328702</v>
@@ -11039,10 +10981,8 @@
       <c r="H115" s="5" t="n">
         <v>0.195928</v>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="5" t="n">
+        <v>0.040705</v>
       </c>
       <c r="J115" s="5" t="n">
         <v>0.394702</v>
@@ -11070,7 +11010,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -11139,10 +11083,8 @@
       <c r="H117" s="5" t="n">
         <v>0.198883</v>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="5" t="n">
+        <v>0.203155</v>
       </c>
       <c r="J117" s="5" t="n">
         <v>0.269254</v>
@@ -11295,10 +11237,8 @@
       <c r="H120" s="5" t="n">
         <v>0.033866</v>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I120" s="5" t="n">
+        <v>0.060302</v>
       </c>
       <c r="J120" s="5" t="n">
         <v>0.065774</v>
@@ -11343,10 +11283,8 @@
       <c r="H121" s="5" t="n">
         <v>0.035993</v>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="5" t="n">
+        <v>0.135779</v>
       </c>
       <c r="J121" s="5" t="n">
         <v>0.207983</v>
@@ -11399,10 +11337,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="5" t="n">
+        <v>4.062351</v>
       </c>
       <c r="J122" s="5" t="n">
         <v>4.683762</v>
@@ -11841,12 +11777,10 @@
         <v>0.055916</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>0.074934</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.074934</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>-0.030795</v>
       </c>
       <c r="J130" s="5" t="n">
         <v>-0.062</v>
@@ -11955,10 +11889,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I132" s="5" t="n">
+        <v>-4.062351</v>
       </c>
       <c r="J132" s="5" t="n">
         <v>-5.47929</v>
@@ -12013,10 +11945,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="J133" s="5" t="n">
         <v>-7e-08</v>
@@ -12067,10 +11997,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="5" t="n">
+        <v>66.899518</v>
       </c>
       <c r="J134" s="5" t="n">
         <v>76.640766</v>
@@ -12097,35 +12025,27 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 6) $</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration costs (Note 5 and 6)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" s="5" t="n">
-        <v>0.05</v>
+        <v>0.124511</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>0.044516</v>
+        <v>1.929772</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.09193999999999999</v>
+        <v>3.381988</v>
       </c>
       <c r="H135" s="5" t="n">
-        <v>0.105709</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.340865</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>2.496918</v>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>2.744171</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -12151,31 +12071,35 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Exploration costs (Note 5 and 6)</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" s="5" t="n">
-        <v>0.124511</v>
-      </c>
-      <c r="F136" s="5" t="n">
-        <v>1.929772</v>
+          <t>Office and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G136" s="5" t="n">
-        <v>3.381988</v>
+        <v>0.121335</v>
       </c>
       <c r="H136" s="5" t="n">
-        <v>4.340865</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.179299</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>0.07367899999999999</v>
+      </c>
+      <c r="J136" s="5" t="n">
+        <v>0.120202</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -12201,39 +12125,33 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Office and administrative expenses</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Share-based payments (Note 6 and 7)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="n">
-        <v>0.121335</v>
-      </c>
-      <c r="H137" s="5" t="n">
-        <v>0.179299</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F137" s="5" t="n">
+        <v>1.573784</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>0.390941</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>0.286218</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -12254,23 +12172,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Property investigation (Note 6)</t>
+          <t>Write-off of mineral properties (Note 5)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" s="5" t="n">
-        <v>0.245219</v>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>0.182684</v>
-      </c>
-      <c r="G138" s="5" t="n">
-        <v>0.14069</v>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -12282,10 +12206,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J138" s="5" t="n">
+        <v>-0.795528</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -12311,30 +12233,28 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 7)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Consulting fees (Note 6) $</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>0.044516</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>1.974385</v>
+        <v>0.09193999999999999</v>
       </c>
       <c r="H139" s="5" t="n">
-        <v>0.61671</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.105709</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>0.107707</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -12365,30 +12285,28 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E140" s="5" t="n">
-        <v>-0.92714</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>-5.250277</v>
+          <t>Share-based payments (Note 7)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>-8.198229</v>
+        <v>1.974385</v>
       </c>
       <c r="H140" s="5" t="n">
-        <v>-6.240478</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.61671</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>0.390941</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -12419,32 +12337,28 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Write-off of abandoned mineral property (Note 5)</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>-0.92714</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>-5.214883</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>-0.323725</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.466037999999999</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>-6.165544</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>-4.062351</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -12475,30 +12389,28 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Basic and diluted loss per common share $</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>-0.92714</v>
+        <v>-7e-08</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>-5.214883</v>
+        <v>-1.6e-07</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>-8.466037999999999</v>
+        <v>-1.4e-07</v>
       </c>
       <c r="H142" s="5" t="n">
-        <v>-6.165544</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9e-08</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -12529,30 +12441,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" s="5" t="n">
-        <v>-7e-08</v>
+        <v>13.806137</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>-1.6e-07</v>
+        <v>32.884329</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>-1.4e-07</v>
+        <v>62.112887</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>-9e-08</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>66.669381</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>66.899518</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -12583,21 +12489,23 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Property investigation (Note 6)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" s="5" t="n">
-        <v>13.806137</v>
+        <v>0.245219</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>32.884329</v>
+        <v>0.182684</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>62.112887</v>
-      </c>
-      <c r="H144" s="5" t="n">
-        <v>66.669381</v>
+        <v>0.14069</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -12633,25 +12541,25 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Directors fees (Note 6)</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E145" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.92714</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.250277</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>-8.198229</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>-6.240478</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -12687,7 +12595,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Listing fees</t>
+          <t>Write-off of abandoned mineral property (Note 5)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -12696,13 +12604,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F146" s="5" t="n">
-        <v>0.109381</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>-0.323725</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -12743,15 +12651,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Office expense</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>Directors fees (Note 6)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E147" s="5" t="n">
-        <v>0.005181</v>
+        <v>0.018</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>0.042958</v>
+        <v>0.042</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -12797,7 +12709,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 6 and 7)</t>
+          <t>Listing fees</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -12807,7 +12719,7 @@
         </is>
       </c>
       <c r="F148" s="5" t="n">
-        <v>1.573784</v>
+        <v>0.109381</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -12853,48 +12765,106 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
+          <t>Office expense</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>0.005181</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>0.042958</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
           <t>Transfer agent and filing fees</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F149" s="5" t="n">
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="n">
         <v>0.007587</v>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
         <is>
           <t>-</t>
         </is>
